--- a/DB/問題と選択肢/questions_tsv変更用.xlsx
+++ b/DB/問題と選択肢/questions_tsv変更用.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\java09\Desktop\trainingmemo\ポートフォリオ\FE-portfolio\DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\java09\Desktop\trainingmemo\ポートフォリオ\FE-portfolio\DB\問題と選択肢\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054194BF-1A71-464E-AEF1-35A4FCB5932F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11A7F8A4-9286-4AD7-9A02-65EE70EA7E66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="choices" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3747,34 +3748,7 @@
       <t>オコナ</t>
     </rPh>
     <rPh sb="150" eb="152">
-      <t>セイカイ</t>
-    </rPh>
-    <rPh sb="180" eb="181">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="183" eb="184">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="189" eb="190">
-      <t>シン</t>
-    </rPh>
-    <rPh sb="191" eb="192">
-      <t>オドロ</t>
-    </rPh>
-    <rPh sb="205" eb="206">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="209" eb="210">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="220" eb="221">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="224" eb="226">
-      <t>ヨハク</t>
-    </rPh>
-    <rPh sb="227" eb="228">
-      <t>セマ</t>
+      <t>セイカイコタシンオドロコタカヨハクセマ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
